--- a/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/03_CMP3 - Tedarikçi ve Dış Kaynak Yönetimi/EKG-STN-FRM-03_tiern_risk_siniflandirmasi_ve_yillik_gozden_gecirme_for.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/03_CMP3 - Tedarikçi ve Dış Kaynak Yönetimi/EKG-STN-FRM-03_tiern_risk_siniflandirmasi_ve_yillik_gozden_gecirme_for.xlsx
@@ -1035,7 +1035,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-FRM-03&amp;C&amp;"Arial,Regular"&amp;11Tier-N Risk Sınıflandırması ve Yıllık Gözden Geçirme Formu (GSON-011)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde5700ac24e84dc2"/>
   <x:tableParts count="1">
@@ -1386,7 +1387,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-FRM-03&amp;C&amp;"Arial,Regular"&amp;11Tier-N Risk Sınıflandırması ve Yıllık Gözden Geçirme Formu (GSON-011)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5776a0e49db4d8b"/>
   <x:tableParts count="1">
